--- a/data/trans_orig/CAGE-Clase-trans_orig.xlsx
+++ b/data/trans_orig/CAGE-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2007</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>469105</t>
+          <t>469070</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>301037</t>
+          <t>301748</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>774567</t>
+          <t>774576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,77 +1548,77 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5122</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4875</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>6781</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>2115</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>7351</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>359545</t>
+          <t>359121</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>366990</t>
+          <t>366743</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>729666</t>
+          <t>730639</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>737829</t>
+          <t>737836</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>840</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>531839</t>
+          <t>532169</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>540665</t>
+          <t>540687</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167782</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>700044</t>
+          <t>699909</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>708488</t>
+          <t>708400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>889</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12625</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,82 +2681,82 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>8266</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>7688</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2972</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>15272</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>9187</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>7688</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>15103</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1217203</t>
+          <t>1216209</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1231638</t>
+          <t>1231134</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>705098</t>
+          <t>706019</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1926482</t>
+          <t>1927305</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1943754</t>
+          <t>1943809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>341232</t>
+          <t>341555</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>349634</t>
+          <t>349583</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>557311</t>
+          <t>558754</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>567738</t>
+          <t>567734</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>903911</t>
+          <t>904297</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>916294</t>
+          <t>916052</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>292901</t>
+          <t>292787</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1243258</t>
+          <t>1243643</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1540655</t>
+          <t>1540671</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14460</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7588</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>17653</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>21627</t>
+          <t>22227</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14331</t>
+          <t>13721</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>31234</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3232599</t>
+          <t>3231864</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3253610</t>
+          <t>3252774</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3360175</t>
+          <t>3360441</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3374150</t>
+          <t>3374207</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,47 +4536,47 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>99,88%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>6470</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>6613387</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>6599463</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>6623701</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
           <t>99,47%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>6470</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>6613387</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>6599240</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>6623163</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2012</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -5063,12 +5063,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>918</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>421643</t>
+          <t>420950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>433501</t>
+          <t>433421</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>312329</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>314454</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>734930</t>
+          <t>734750</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>747974</t>
+          <t>748518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17354</t>
+          <t>18063</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>401361</t>
+          <t>402938</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>417812</t>
+          <t>417807</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>332298</t>
+          <t>331634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>738930</t>
+          <t>739244</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>754689</t>
+          <t>754645</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>857</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14329</t>
+          <t>13193</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>15459</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>607560</t>
+          <t>606256</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>623626</t>
+          <t>623219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>258091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>260129</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>867125</t>
+          <t>866801</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>883806</t>
+          <t>883687</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>19718</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1123306</t>
+          <t>1124756</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1143636</t>
+          <t>1144066</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>761679</t>
+          <t>760644</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1890880</t>
+          <t>1889624</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1910880</t>
+          <t>1910082</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>738</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>493747</t>
+          <t>493832</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>505833</t>
+          <t>505973</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>755444</t>
+          <t>754366</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1252587</t>
+          <t>1252512</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1266347</t>
+          <t>1265747</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12158</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>252333</t>
+          <t>253658</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>263877</t>
+          <t>263935</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1104409</t>
+          <t>1104397</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1360930</t>
+          <t>1361024</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1372925</t>
+          <t>1372360</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8414,47 +8414,47 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>8882</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>4373</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>16306</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>8882</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>4413</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>16388</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>33506</t>
+          <t>34276</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35167</t>
+          <t>36537</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>24787</t>
+          <t>25014</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>51630</t>
+          <t>50702</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>28751</t>
+          <t>28284</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>56058</t>
+          <t>55002</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3336514</t>
+          <t>3335759</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3371997</t>
+          <t>3371861</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3538717</t>
+          <t>3539020</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3548131</t>
+          <t>3548134</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6881160</t>
+          <t>6881033</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6918394</t>
+          <t>6917548</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2016</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9217,12 +9217,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16817</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>415702</t>
+          <t>415804</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>428007</t>
+          <t>428028</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>335754</t>
+          <t>335012</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>758347</t>
+          <t>757769</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>772408</t>
+          <t>772415</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -9736,12 +9736,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>367811</t>
+          <t>368581</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>376292</t>
+          <t>376311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10090,49 +10090,49 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>369092</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>363175</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>371331</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>369092</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>363254</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>371333</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>700</t>
@@ -10145,12 +10145,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>736730</t>
+          <t>735922</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>747313</t>
+          <t>746877</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -10418,12 +10418,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>905</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>908</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13032</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -10644,12 +10644,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>505618</t>
+          <t>504915</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>517770</t>
+          <t>517915</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158806</t>
+          <t>159032</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>669136</t>
+          <t>668115</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>682699</t>
+          <t>682463</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>23381</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11135,12 +11135,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>826</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26885</t>
+          <t>26389</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1121993</t>
+          <t>1121751</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1139520</t>
+          <t>1139911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>817872</t>
+          <t>817573</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>825053</t>
+          <t>825050</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1944666</t>
+          <t>1943303</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1963838</t>
+          <t>1963216</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -11669,12 +11669,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>604162</t>
+          <t>603898</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>616593</t>
+          <t>616854</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>732746</t>
+          <t>731862</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -11832,39 +11832,39 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>1348887</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>1340391</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>1353962</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
           <t>99,26%</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>1287</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>1348887</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>1340327</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>1354033</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
           <t>98,63%</t>
@@ -11872,7 +11872,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -12012,12 +12012,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -12125,12 +12125,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -12238,12 +12238,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14426</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>274510</t>
+          <t>273976</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>285105</t>
+          <t>284357</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1072322</t>
+          <t>1072273</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1081079</t>
+          <t>1081074</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1352555</t>
+          <t>1352341</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1364406</t>
+          <t>1364434</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9612</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21653</t>
+          <t>22232</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>23126</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23884</t>
+          <t>23120</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>47853</t>
+          <t>48460</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>23516</t>
+          <t>23876</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>35393</t>
+          <t>35651</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>65606</t>
+          <t>64962</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3319930</t>
+          <t>3321715</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3348959</t>
+          <t>3350336</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3503306</t>
+          <t>3505505</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3521561</t>
+          <t>3521858</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6831814</t>
+          <t>6832818</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6865654</t>
+          <t>6866678</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2023</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13389,7 +13389,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -13610,12 +13610,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13680,12 +13680,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13695,12 +13695,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>266755</t>
+          <t>267828</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>277150</t>
+          <t>277485</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13758,12 +13758,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>152223</t>
+          <t>151968</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157607</t>
+          <t>157601</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>423914</t>
+          <t>423443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>434083</t>
+          <t>434351</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14003,12 +14003,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -14066,12 +14066,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14116,12 +14116,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14136,12 +14136,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14151,12 +14151,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -14292,12 +14292,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>205971</t>
+          <t>205659</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>211493</t>
+          <t>211495</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>125312</t>
+          <t>125147</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>130800</t>
+          <t>130841</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14362,12 +14362,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>333848</t>
+          <t>333917</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>341303</t>
+          <t>341300</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -14522,12 +14522,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14537,12 +14537,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14557,12 +14557,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14572,12 +14572,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14592,12 +14592,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14607,12 +14607,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -14635,12 +14635,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14650,12 +14650,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14705,12 +14705,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14720,12 +14720,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -14748,12 +14748,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>9843</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14783,12 +14783,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14798,12 +14798,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>981</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -14861,12 +14861,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198536</t>
+          <t>199922</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208951</t>
+          <t>209410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14896,12 +14896,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39214</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>239121</t>
+          <t>238186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249203</t>
+          <t>249126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -14946,12 +14946,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15106,12 +15106,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15161,12 +15161,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15176,12 +15176,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -15204,12 +15204,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15254,12 +15254,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15274,12 +15274,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12176</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -15317,12 +15317,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16317</t>
+          <t>17123</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15352,12 +15352,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15367,12 +15367,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15387,12 +15387,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>909</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15407,7 +15407,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -15430,12 +15430,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>482849</t>
+          <t>482973</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>501263</t>
+          <t>500862</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15445,12 +15445,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>405619</t>
+          <t>405699</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -15480,7 +15480,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -15500,12 +15500,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>892789</t>
+          <t>891783</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>914150</t>
+          <t>914070</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15515,12 +15515,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -15660,12 +15660,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>8798</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15675,12 +15675,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15695,12 +15695,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>539</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15730,12 +15730,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15745,12 +15745,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -15773,12 +15773,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15823,12 +15823,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15843,12 +15843,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7701</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15858,12 +15858,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15956,12 +15956,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>164</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>217733</t>
+          <t>216727</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>227444</t>
+          <t>227620</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>124699</t>
+          <t>124890</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>130093</t>
+          <t>130142</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16049,12 +16049,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16069,12 +16069,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>345224</t>
+          <t>344782</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>356742</t>
+          <t>356012</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16084,12 +16084,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -16229,12 +16229,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16244,12 +16244,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -16342,12 +16342,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16357,12 +16357,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16377,12 +16377,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16392,12 +16392,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16412,12 +16412,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16427,12 +16427,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16470,12 +16470,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16490,12 +16490,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16505,12 +16505,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16525,12 +16525,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16540,12 +16540,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -16568,12 +16568,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>90330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16583,12 +16583,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16603,7 +16603,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>205066</t>
+          <t>205707</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -16798,12 +16798,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18936</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16813,82 +16813,82 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>7642</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>3241</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>16730</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>19434</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>11442</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>29854</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>7642</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>2724</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>16055</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>19434</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>11803</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>29444</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16946,12 +16946,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16961,12 +16961,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19757</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16996,12 +16996,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -17024,12 +17024,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>23879</t>
+          <t>23940</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17039,12 +17039,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17059,12 +17059,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>27363</t>
+          <t>25700</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17109,12 +17109,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -17137,12 +17137,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1487761</t>
+          <t>1489646</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1512579</t>
+          <t>1513005</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17152,12 +17152,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17172,12 +17172,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>974365</t>
+          <t>974350</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>989235</t>
+          <t>989133</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17192,7 +17192,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2467414</t>
+          <t>2468222</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2498740</t>
+          <t>2499877</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17222,12 +17222,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CAGE-Clase-trans_orig.xlsx
+++ b/data/trans_orig/CAGE-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>469070</t>
+          <t>469065</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>301748</t>
+          <t>302096</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>774576</t>
+          <t>773573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>359121</t>
+          <t>359622</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>366743</t>
+          <t>366647</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>730639</t>
+          <t>730515</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>737836</t>
+          <t>737839</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>845</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>532169</t>
+          <t>532246</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>540687</t>
+          <t>540677</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>699909</t>
+          <t>700179</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>708400</t>
+          <t>708548</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>890</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12474</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15272</t>
+          <t>16248</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1216209</t>
+          <t>1216281</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1231134</t>
+          <t>1231150</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>706019</t>
+          <t>705315</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1927305</t>
+          <t>1926360</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1943809</t>
+          <t>1943398</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13676</t>
+          <t>13024</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>341555</t>
+          <t>341031</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>349583</t>
+          <t>349644</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>558754</t>
+          <t>558262</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>567734</t>
+          <t>567725</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>904297</t>
+          <t>903822</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>916052</t>
+          <t>915663</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>292787</t>
+          <t>291761</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1243643</t>
+          <t>1243375</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1540671</t>
+          <t>1539613</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12576</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15326</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>17653</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>22227</t>
+          <t>22378</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>14245</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>31234</t>
+          <t>29619</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3231864</t>
+          <t>3232459</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3252774</t>
+          <t>3253992</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,82 +4501,82 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>3288</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>3368835</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>3359980</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3373972</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>99,88%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>6470</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>6613387</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>6598877</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>6623007</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
           <t>99,47%</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>3288</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>3368835</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>3360441</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>3374207</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>6470</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>6613387</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>6599463</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>6623701</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -5063,12 +5063,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12776</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -5176,82 +5176,82 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>919</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7714</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2845</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>917</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7610</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>2845</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>420950</t>
+          <t>421131</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>433421</t>
+          <t>433498</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>734750</t>
+          <t>734456</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>748518</t>
+          <t>747952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>16349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18063</t>
+          <t>19347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>402938</t>
+          <t>401434</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>417807</t>
+          <t>417814</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>331634</t>
+          <t>332243</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>739244</t>
+          <t>738118</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>754645</t>
+          <t>754686</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14452</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>848</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13193</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14719</t>
+          <t>14627</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>606256</t>
+          <t>606826</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>623219</t>
+          <t>623620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>866801</t>
+          <t>865137</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>883687</t>
+          <t>883583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>11467</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>14907</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>19193</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19718</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1124756</t>
+          <t>1124410</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1144066</t>
+          <t>1144001</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>760644</t>
+          <t>760970</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1889624</t>
+          <t>1889414</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1910082</t>
+          <t>1909874</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>493832</t>
+          <t>494253</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>505973</t>
+          <t>505970</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>754366</t>
+          <t>754470</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1252512</t>
+          <t>1252652</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1265747</t>
+          <t>1266233</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>12060</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8076,42 +8076,42 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>6173</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>13189</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>6173</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>2286</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>12710</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>253658</t>
+          <t>252677</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>263935</t>
+          <t>263917</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1104397</t>
+          <t>1103889</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1361024</t>
+          <t>1360995</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1372360</t>
+          <t>1372480</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16306</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>12263</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>34276</t>
+          <t>32160</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36537</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>25014</t>
+          <t>25122</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>50702</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10217</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>28284</t>
+          <t>27900</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>55002</t>
+          <t>55900</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3335759</t>
+          <t>3337766</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3371861</t>
+          <t>3371827</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3539020</t>
+          <t>3538851</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3548134</t>
+          <t>3548133</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6881033</t>
+          <t>6881833</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6917548</t>
+          <t>6918724</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11622</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>11908</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16817</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -9506,12 +9506,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>415804</t>
+          <t>415367</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>428028</t>
+          <t>428026</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>335012</t>
+          <t>335147</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>346131</t>
+          <t>346123</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>757769</t>
+          <t>758727</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>772415</t>
+          <t>772453</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>10560</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>368581</t>
+          <t>368586</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>376311</t>
+          <t>377227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>363175</t>
+          <t>363736</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>371331</t>
+          <t>371334</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>735922</t>
+          <t>736367</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>746877</t>
+          <t>747416</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -10418,12 +10418,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>900</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>13916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -10644,12 +10644,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>504915</t>
+          <t>505098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>517915</t>
+          <t>517799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>159032</t>
+          <t>159636</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>668115</t>
+          <t>669274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>682463</t>
+          <t>682901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9160</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>23242</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11135,12 +11135,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>815</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>9239</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26389</t>
+          <t>27134</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1121751</t>
+          <t>1122088</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1139911</t>
+          <t>1139839</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>817573</t>
+          <t>818186</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>825050</t>
+          <t>825061</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,42 +11263,42 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1955576</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1943828</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1963327</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>98,99%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1955576</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1943303</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1963216</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -11669,12 +11669,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>603898</t>
+          <t>602895</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>616854</t>
+          <t>616588</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>731862</t>
+          <t>732117</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1340391</t>
+          <t>1339980</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1353962</t>
+          <t>1354019</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -12238,12 +12238,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13169</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14426</t>
+          <t>15071</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>273976</t>
+          <t>275129</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>284357</t>
+          <t>284394</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1072273</t>
+          <t>1072474</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1081074</t>
+          <t>1080961</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1352341</t>
+          <t>1351518</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1364434</t>
+          <t>1364326</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22232</t>
+          <t>22325</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24967</t>
+          <t>23791</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23120</t>
+          <t>23134</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>48460</t>
+          <t>46661</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>23876</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>35651</t>
+          <t>35959</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>64962</t>
+          <t>65863</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3321715</t>
+          <t>3322116</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3350336</t>
+          <t>3350185</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3505505</t>
+          <t>3504409</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3521858</t>
+          <t>3521570</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6832818</t>
+          <t>6832285</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6866678</t>
+          <t>6866952</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>868</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -13389,12 +13389,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -13424,12 +13424,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13449,32 +13449,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -13492,32 +13492,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13562,32 +13562,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -13605,102 +13605,102 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3249</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3418</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>5033</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>10818</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>3888</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>8420</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -13718,32 +13718,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>273852</t>
+          <t>292620</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>267828</t>
+          <t>285076</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>277485</t>
+          <t>297165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13753,32 +13753,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>156167</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>151968</t>
+          <t>165142</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157601</t>
+          <t>170219</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13788,32 +13788,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>430019</t>
+          <t>461369</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>423443</t>
+          <t>453908</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>434351</t>
+          <t>466632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -13831,17 +13831,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>280203</t>
+          <t>301063</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>280203</t>
+          <t>301063</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>280203</t>
+          <t>301063</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13866,17 +13866,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>158110</t>
+          <t>170755</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>158110</t>
+          <t>170755</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158110</t>
+          <t>170755</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13901,17 +13901,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>438313</t>
+          <t>471817</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>438313</t>
+          <t>471817</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>438313</t>
+          <t>471817</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -13958,12 +13958,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -14028,12 +14028,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -14096,32 +14096,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>722</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14131,32 +14131,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>730</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>945</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -14184,12 +14184,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>689</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -14254,12 +14254,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>5895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -14287,32 +14287,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>209911</t>
+          <t>220788</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>205659</t>
+          <t>216073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>211495</t>
+          <t>222679</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14322,32 +14322,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>128898</t>
+          <t>139265</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>125147</t>
+          <t>134742</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>130841</t>
+          <t>141487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14357,32 +14357,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>338809</t>
+          <t>360053</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>333917</t>
+          <t>354391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>341300</t>
+          <t>363195</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -14400,17 +14400,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>211662</t>
+          <t>223362</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211662</t>
+          <t>223362</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211662</t>
+          <t>223362</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14435,17 +14435,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>131680</t>
+          <t>142894</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131680</t>
+          <t>142894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131680</t>
+          <t>142894</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14470,17 +14470,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>343342</t>
+          <t>366256</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>343342</t>
+          <t>366256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>343342</t>
+          <t>366256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14517,32 +14517,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14587,32 +14587,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>788</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -14743,32 +14743,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9843</t>
+          <t>14561</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14813,32 +14813,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>13451</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -14856,32 +14856,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>205352</t>
+          <t>220163</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199922</t>
+          <t>210953</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209410</t>
+          <t>224849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -14926,32 +14926,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>245685</t>
+          <t>266728</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>238186</t>
+          <t>258767</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249126</t>
+          <t>271555</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -14969,17 +14969,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15004,17 +15004,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15086,32 +15086,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15121,32 +15121,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15156,32 +15156,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>18054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -15199,32 +15199,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15269,32 +15269,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -15312,32 +15312,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15382,32 +15382,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -15425,32 +15425,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>494509</t>
+          <t>527656</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>482973</t>
+          <t>518456</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>500862</t>
+          <t>533450</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15460,32 +15460,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>409831</t>
+          <t>223338</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>405699</t>
+          <t>214385</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>411857</t>
+          <t>226472</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15495,32 +15495,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>904340</t>
+          <t>750993</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>891783</t>
+          <t>739172</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>914070</t>
+          <t>757601</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -15538,17 +15538,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>508300</t>
+          <t>540271</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>508300</t>
+          <t>540271</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>508300</t>
+          <t>540271</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15573,17 +15573,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>411857</t>
+          <t>227505</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>411857</t>
+          <t>227505</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>411857</t>
+          <t>227505</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15608,17 +15608,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>920157</t>
+          <t>767776</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>920157</t>
+          <t>767776</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>920157</t>
+          <t>767776</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15655,32 +15655,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15690,32 +15690,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15725,32 +15725,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -15768,32 +15768,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15838,32 +15838,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>586</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>756</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -15926,12 +15926,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15951,32 +15951,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>547</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -15994,32 +15994,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>223824</t>
+          <t>248236</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>216727</t>
+          <t>241055</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>227620</t>
+          <t>252727</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16029,32 +16029,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>128352</t>
+          <t>150318</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>124890</t>
+          <t>146758</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>130142</t>
+          <t>152061</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16064,32 +16064,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>352178</t>
+          <t>398554</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>344782</t>
+          <t>390981</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>356012</t>
+          <t>403505</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -16107,17 +16107,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>231133</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>231133</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>231133</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16142,17 +16142,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16177,17 +16177,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>362257</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>362257</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>362257</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16209,7 +16209,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -16259,7 +16259,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -16304,12 +16304,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16563,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -16598,27 +16598,27 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>119174</t>
+          <t>124247</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>114842</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -16633,27 +16633,27 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>214034</t>
+          <t>210088</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>205707</t>
+          <t>201033</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -16676,17 +16676,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16711,17 +16711,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -16746,17 +16746,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -16793,32 +16793,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16828,32 +16828,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16863,32 +16863,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>15177</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>29854</t>
+          <t>34782</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -16906,17 +16906,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>18575</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16941,32 +16941,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>803</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16976,32 +16976,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>12022</t>
+          <t>13460</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -17019,32 +17019,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>23940</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17054,32 +17054,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17089,32 +17089,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>25700</t>
+          <t>30328</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -17132,67 +17132,67 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1502308</t>
+          <t>1595303</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1489646</t>
+          <t>1579956</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1513005</t>
+          <t>1607321</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>852482</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>840461</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>858596</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
           <t>96,89%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>1150</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>982756</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>974350</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>989133</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17202,32 +17202,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2485064</t>
+          <t>2447783</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2468222</t>
+          <t>2430469</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2499877</t>
+          <t>2461225</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -17245,17 +17245,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1537453</t>
+          <t>1635640</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1537453</t>
+          <t>1635640</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1537453</t>
+          <t>1635640</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17280,17 +17280,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>994505</t>
+          <t>867437</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>994505</t>
+          <t>867437</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>994505</t>
+          <t>867437</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17315,17 +17315,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2531958</t>
+          <t>2503076</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2531958</t>
+          <t>2503076</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2531958</t>
+          <t>2503076</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
